--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="356">
   <si>
     <t>Link</t>
   </si>
@@ -32,19 +32,1189 @@
   </si>
   <si>
     <t>Selection Process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/alfred-armbrust-memorial-bursary
+</t>
+  </si>
+  <si>
+    <t>Alfred Armbrust Memorial Bursary</t>
+  </si>
+  <si>
+    <t>Several bursaries, of varying amounts are awarded annually to full-time undergraduate students in the Faculty of Engineering who are experiencing financial difficulties.</t>
+  </si>
+  <si>
+    <t>Application required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/alyson-woloshyn-leadership-award
+</t>
+  </si>
+  <si>
+    <t>Alyson Woloshyn Leadership Award</t>
+  </si>
+  <si>
+    <t>One or more awards, valued at $1,000 each, are provided annually to full-time undergraduate students enrolled in Year Three or Four of any program who have made significant leadership contributions to the student experience through involvement with activities such as student government, Varsity Athletics, Orientation, and/or Residence Life. Candidates must have a minimum overall average of 75%. Interested students should submit an application by November1. This fund is made possible by a donation from friends and family of the late Alyson Woloshyn to celebrate the living legacy of a woman who constantly moved people from dreaming to achieving.</t>
+  </si>
+  <si>
+    <t>$1,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/barkleys-avonmore-bursary
+</t>
+  </si>
+  <si>
+    <t>Barkley's of Avonmore Bursary</t>
+  </si>
+  <si>
+    <t>One bursary is awarded annually to a student from a Third World Country. Interested international students must submit a bursary application form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/bateman-minello-award
+</t>
+  </si>
+  <si>
+    <t>Bateman-Minello Award</t>
+  </si>
+  <si>
+    <t>An award, valued at $10,000, will be provided to a full-time undergraduate student enrolled in Year Two, Three, or Four of any program in the Faculty of Engineering. Selection is based on positive contributions to the 2SLGBTQ+ community through extracurricular or volunteer involvement. Interested students should submit an application by October 1. This fund is made possible by a donation from the Bateman Minello Family Foundation to support and celebrate the 2SLGBTQ+ community.</t>
+  </si>
+  <si>
+    <t>$10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/bayne-international-experience-award
+</t>
+  </si>
+  <si>
+    <t>Bayne International Experience Award</t>
+  </si>
+  <si>
+    <t>An award, valued at $1,000, will be provided annually to a full-time undergraduate student enrolled in Year Two, Three, or Four of Computer Engineering or Software Engineering who will be participating in an international study or co-op work experience. Candidates must have a minimum cumulative average of 80%. Preference will be given to students travelling to an unfamiliar country where they will experience a different culture. Interested students must submit the general UW International Experience Award application by November 15. This fund is made possible by a donation from Chad Bayne and his family to encourage students to pursue an international experience.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/bernice-maccallum-hilliard-bursary
+</t>
+  </si>
+  <si>
+    <t>Bernice MacCallum Hilliard Bursary</t>
+  </si>
+  <si>
+    <t>Bursaries, of varying value, are awarded annually to mature, undergraduate students who identify as women, enrolled in full- or part-time studies at the University of Waterloo, who are in need of financial assistance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/bernie-roehl-award
+</t>
+  </si>
+  <si>
+    <t>Bernie Roehl Award</t>
+  </si>
+  <si>
+    <t>This award has been established by Max and Ann Roehl in honour of their son, Bernie Roehl, (BSc 1983), a proud graduate and current Waterloo staff member. One award, valued at up to $1,000, will be made to an undergraduate student entering second-, third-, or fourth-year Electrical &amp; Computer Engineering or Software Engineering who has an above average academic standing and who can demonstrate an involvement with university extracurricular activities such as amateur theatre, student government (e.g. Federation of Students) or the student radio station.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/cupe-local-793-award
+</t>
+  </si>
+  <si>
+    <t>C.U.P.E. Local 793 Award</t>
+  </si>
+  <si>
+    <t>several awards available each year</t>
+  </si>
+  <si>
+    <t>$500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/cae-inc-award-software-engineering
+</t>
+  </si>
+  <si>
+    <t>CAE Inc. Award in Software Engineering</t>
+  </si>
+  <si>
+    <t>Several awards, valued at $1,000 or more each, will be presented annually to full-time undergraduate students enrolled in any year of the Software Engineering program who have a minimum overall average of 75% and who have a demonstrated financial need. To be considered, students must complete the University of Waterloo Full-Time Bursary Application. This fund is made possible by a generous gift from CAE Inc. to support students in their academic pursuits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/caivan-future-cities-undergraduate-scholarship
+</t>
+  </si>
+  <si>
+    <t>Caivan Future Cities Undergraduate Scholarship</t>
+  </si>
+  <si>
+    <t>Ira G. Needles Hall (NH)</t>
+  </si>
+  <si>
+    <t>$2,500</t>
+  </si>
+  <si>
+    <t>Students considered automatically - no application.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/campus-recreation-bursary
+</t>
+  </si>
+  <si>
+    <t>Campus Recreation Bursary</t>
+  </si>
+  <si>
+    <t>This bursary may be awarded annually to a student, or students, who display strong leadership contribution to the Campus Recreation programs. Candidates must be in good academic standing and have demonstrated financial need.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/canadian-friends-hebrew-university-travel-award
+</t>
+  </si>
+  <si>
+    <t>Canadian Friends of the Hebrew University Travel Award</t>
+  </si>
+  <si>
+    <t>This fund was established to assist University of Waterloo students who are approved to participate in a study abroad program at the Hebrew University of Jerusalem or the Rothberg International School in Israel and who have demonstrated financial need.  Undergraduate and graduate students in all faculties and programs, who are in good academic standing, are invited to apply.  Candidates must be Canadian citizens or permanent residents and have lived in Ontario for the entire 12-month period prior to beginning their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/canadian-imperial-bank-commerce-award
+</t>
+  </si>
+  <si>
+    <t>Canadian Imperial Bank of Commerce Award</t>
+  </si>
+  <si>
+    <t>One or more awards, valued at $1,000 each, have been established by the Canadian Imperial Bank of Commerce to assist students in financial need. Full-time undergraduates in any Faculty who have maintained a minimum overall average of 75% and who are experiencing financial difficulties may apply. Eligible students must have resided in Ontario for 12 months prior to the beginning of their post-secondary education. Preference will be given to students who demonstrate leadership ability as shown through on-campus or community extracurricular activities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/canadian-nuclear-laboratories-cnl-undergraduate-engineering
+</t>
+  </si>
+  <si>
+    <t>Canadian Nuclear Laboratories (CNL) Undergraduate Engineering Scholarship</t>
+  </si>
+  <si>
+    <t>A scholarship, valued at $10,000, will be awarded annually to a full-time undergraduate student enrolled in Year Two, Three, or Four of any program in the Faculty of Engineering (excluding the School of Architecture). Selection is based on academic excellence (minimum 80% cumulative average), combined with a demonstrated interest in the nuclear sector as shown through extracurricular involvement, research projects, co-op work terms, and special projects. Interested students should submit an application by October 1. This scholarship is made possible by Canadian Nuclear Laboratories (CNL) to foster the next generation of engineering talent for Canada’s nuclear sector.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/canadian-posture-seating-centre-award-project-funding
+</t>
+  </si>
+  <si>
+    <t>Canadian Posture &amp; Seating Centre Award for Project Funding</t>
+  </si>
+  <si>
+    <t>This fund was established to encourage student interest in and attainment of academic and practical achievements focused on the development and delivery of systems, methodology or assistive devices that facilitate full participation in Canadian society by physically disadvantaged persons.  Awards are normally valued at between $500 and $2,000 may be granted to students or teams who are involved in a student project directed toward delivery of such services. Interested students in third- or fourth-year may apply.  The mean of the averages of all students working on the project must be 75% minimum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/canadian-posture-seating-centre-scholarship
+</t>
+  </si>
+  <si>
+    <t>Canadian Posture &amp; Seating Centre Scholarship</t>
+  </si>
+  <si>
+    <t>This fund was established to recognize and encourage student interest in and attainment of a high level of academic and practical achievement in preparation for development and delivery of systems, methodology or assistive devices that facilitate full participation in Canadian society by physically disadvantaged persons. Scholarships, normally valued between $1,000 and $2,500, may be awarded to outstanding students (minimum 80% overall average) who demonstrate an interest and ability in engineering and business directed toward delivery of such services. Interested Engineering students in second- third- or fourth-year or in Graduate Studies are invited to apply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/carlisle-engineering-scholarship
+</t>
+  </si>
+  <si>
+    <t>Carlisle Engineering Scholarship</t>
+  </si>
+  <si>
+    <t>A scholarship, valued at up to $1,500, will be provided annually to a full-time undergraduate student enrolled in Year Two, Three, or Four of any program in the Faculty of Engineering (excluding School of Architecture). Selection is based on academic excellence (minimum 80% cumulative average) combined with extracurricular involvement and/or participation in volunteer activities related to the field of engineering. Interested students should submit an application by October 1. This fund is made possible by a donation from Stephen Carlisle (BASc '86) to support future Waterloo engineers.</t>
+  </si>
+  <si>
+    <t>$1,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/co-op-problem-award
+</t>
+  </si>
+  <si>
+    <t>Co-op Problem Award</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/co-op-student-year-award
+</t>
+  </si>
+  <si>
+    <t>Co-op Student of the Year Award</t>
+  </si>
+  <si>
+    <t>Each year, a student from each Faculty will be awarded the Co-op Student of the Year Award. Selection is based on exceptional contributions to one or more of their work-term employers. An honourable mention designation will be provided to the second-place winner from each Faculty. Consideration for these awards is by application or nomination - full details are available on the Co-operative Education website.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/collective-movement-award-community-leadership
+</t>
+  </si>
+  <si>
+    <t>Collective Movement Award for Community Leadership</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,200, is provided annually to a full-time undergraduate student enrolled in Year Two, Three or Four in any Faculty. Students must be in good academic standing and must submit an essay (500-1,000 words) describing the positive impact they have had to the African, Caribbean or Black communities within Canada through extracurricular or volunteer involvement. Interested students should submit an application by November 1. This endowment fund was founded by Michael C. Robson and is made possible by donations from individuals and business who are part of the African, Caribbean, or Black communities in Canada, or who are advocates for these communities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/colonel-gerry-mann-memorial-bursary
+</t>
+  </si>
+  <si>
+    <t>Colonel Gerry Mann Memorial Bursary</t>
+  </si>
+  <si>
+    <t>One bursary, valued at approximately $1,000, is awarded annually to a full-time undergraduate student enrolled in any program who is in good academic standing (minimum overall average of 70%) and who has a demonstrated financial need, as determined by Waterloo. To be considered, students must complete the Full-time Bursary/Award application. Preference will be given to students who identify career goals in the Canadian military, law enforcement, or aviation, as well as to students with demonstrated leadership skills. This fund is made possible through donations from Tina Mann, Jack Trimmer, and family and friends in honour and memory of Tina’s father Colonel Gerry Mann.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/convera-bursary
+</t>
+  </si>
+  <si>
+    <t>Convera Bursary</t>
+  </si>
+  <si>
+    <t>A bursary, valued at $1,200, will be awarded annually to a full-time international undergraduate student enrolled in Year, Two, Three, or Four in any Faculty who is in good academic standing, and who has demonstrated financial need as determined by Waterloo. To be considered, students must complete a bursary application by the fall-term deadline. This fund is made possible by a donation from Western Union Business Solutions, now known as Convera.</t>
+  </si>
+  <si>
+    <t>$1,200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/croatian-travel-awards
+</t>
+  </si>
+  <si>
+    <t>Croatian Travel Awards</t>
+  </si>
+  <si>
+    <t>Travel funds, valued at up to $1,500, are available for undergraduate and/or graduate students registered at the University of Waterloo who participate in a recognized Croatian language or cultural study abroad program, an exchange program, or an approved co-op term in Croatia. Selection will be based on a statement describing their intended Croatian experience and why they hope to receive this funding. Interested students may submit an international experience award application found on the Student Awards &amp; Financial Aid website or Graduate Studies and Postdoctoral Affairs website by March 15 or Nov. 15 for an upcoming experience.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/cybersecurity-and-privacy-institute-undergraduate-award
+</t>
+  </si>
+  <si>
+    <t>Cybersecurity and Privacy Institute Undergraduate Award</t>
+  </si>
+  <si>
+    <t>Several awards, valued at $1,000 each, will be presented to full-time undergraduate students enrolled in cybersecurity and/or privacy courses. Selection will be based on overall grade in the course. These awards are made possible by sponsorships to the Cybersecurity and Privacy Institute to address the cybersecurity/privacy talent gap by fostering student enrolment in cybersecurity/privacy courses and encouraging more students to consider a career in this field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/dan-and-anik-colquhoun-award
+</t>
+  </si>
+  <si>
+    <t>Dan and Anik Colquhoun Award</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An award, valued at $2,500, will be provided annually to a full-time undergraduate student enrolled in Year Three or Four of Computer, Electrical, or Systems Design Engineering who can demonstrate that they have overcome a personal or medical challenge. Interested students should submit an application by October 1. This fund is made possible by a donation from Daniel and Anik Colquhoun. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/david-johnston-lebovic-foundation-international-experience
+</t>
+  </si>
+  <si>
+    <t>David Johnston - Lebovic Foundation International Experience Awards</t>
+  </si>
+  <si>
+    <t>Several awards are provided annually to full-time undergraduate and graduate students in any Faculty who participate in an international experience in Israel, including a minimally-paid or volunteer co-op work placement, a volunteer placement, or a study term related to academic requirements. Awards are valued at up to $2,500 - $10,000 each, and will be given on the basis of academic achievement, as well as the type and duration of the experience. Interested students, in good academic standing (normally a minimum 70% average at the undergraduate level; normally a minimum 75% average at the graduate level), who are planning to participate in an international experience in Israel are eligible to apply. Award selection will take place once per term. Students should apply as soon as they are able to confirm the details of their intended experience by one of the following deadlines: July 15, November 15, or March 15. These awards were established through the generous support of the Joseph and Wolf Lebovic Foundation in honour of former Waterloo President David Johnston, as a lasting tribute to his 11-year service to this university and in recognition of his passion for international opportunities for students.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/david-johnston-international-experience-awards
+</t>
+  </si>
+  <si>
+    <t>David Johnston International Experience Awards</t>
+  </si>
+  <si>
+    <t>Several awards are provided annually to full-time undergraduate and graduate students in any Faculty who wish to participate in an international experience, including a minimally-paid or volunteer international co-op work placement, a volunteer placement, an academic exchange or a study term related to academic requirements. Selection is based on a combination of academic achievement and the location and duration of the international experience. Preference will be given to students who will be travelling to an unfamiliar country where they will experience a different culture in a new learning environment.  These awards were established through the generous support of donors in honour of former Waterloo President David Johnston as a lasting tribute to his 11-year service to this university and in recognition of his passion for international opportunities for students.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/david-johnston-waterloo-awards-refugee-students
+</t>
+  </si>
+  <si>
+    <t>David Johnston Waterloo Awards for Refugee Students</t>
+  </si>
+  <si>
+    <t>Funding is available each year to support undergraduate and graduate refugee students who are sponsored by the World University Service of Canada at Waterloo (WUSC) or any other students who are recognized by the Canadian government as being refugees or protected persons. Candidates may be enrolled in any Faculty/program at the University of Waterloo. The funds are intended to assist students who are no longer receiving sponsorship support and who have a demonstrated financial need. Candidates must be in satisfactory academic standing. The value of each award will vary depending on financial need and available funds. These awards were established through the generous support of donors in honour of former Waterloo President David Johnston as a lasting tribute to his 11-year service to this university and in recognition of his passion for international opportunities for students.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/douglas-k-campbell-memorial-bursary
+</t>
+  </si>
+  <si>
+    <t>Douglas K. Campbell Memorial Bursary</t>
+  </si>
+  <si>
+    <t>A bursary, valued at approximately $1,000, is awarded annually to a full-time undergraduate student enrolled in any year and any program who is in good academic standing, and who has a demonstrated financial need as determined by UW. To be considered, students must complete the UW Full-time Bursary Application. Preference will be given to candidates whose parent or parents are members of a trade union. For the purpose of this bursary, a trade union is an association of workers from any sector of the workforce in Canada that has been certified by applicable legislation to represent employees in the negotiation of the terms of their employment. This fund is made possible by a donation from the estate of Douglas K. Campbell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/douglas-t-wright-award
+</t>
+  </si>
+  <si>
+    <t>Douglas T. Wright International Co-op Award</t>
+  </si>
+  <si>
+    <t>Three awards, valued at up to $1,500 each, are provided annually to support undergraduate students enrolled in second-, third-, or fourth-year of any program who are pursuing a co-op work term outside of Canada. A minimum overall average of 75% is required. Preference will be given to students travelling to an unfamiliar country where they will experience a different culture and to students receiving low salary/compensation while abroad. Interested students are to apply in the term prior to the work experience, by March 15, July 15, or November 15. This fund was established in 1993 by members of the University community to honour Douglas T. Wright upon his retirement as president of the University and to recognize his contribution to the University's international reputation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/dr-stanley-f-leavine-scholarship
+</t>
+  </si>
+  <si>
+    <t>Dr. Stanley F. Leavine Scholarship</t>
+  </si>
+  <si>
+    <t>A scholarship, valued at $2,500, is provided annually to an outstanding third- or fourth-year undergraduate student enrolled in any program who has a demonstrated interest in pursuing a career in medicine or medical research, as evidenced by work or volunteer experiences and/or involvement in entrepreneurial activities related to medical innovation. Candidates must have a minimum overall average of 80% or more. An application is required by November 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/drysdale-international-experience-award
+</t>
+  </si>
+  <si>
+    <t>Drysdale International Experience Award</t>
+  </si>
+  <si>
+    <t>An award, valued up to $2,500, is available annually to a full-time undergraduate student enrolled in Year Two, Three, or Four in any Faculty, who is embarking on an international work, volunteer, or study experience related to academic requirements. Selection is on the basis of academic achievement (minimum 75%), and the location, duration, and type of international experience. Preference will be given to students with financial need who will be travelling to an unfamiliar country where they will experience a different culture in a new learning environment. Interested students should submit an application by November 15. This award is made possible by a generous donation from the Drysdale Family in recognition of their commitment to ongoing experiential education, international learning opportunities, and active global citizenship.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/dupont-peppler-award-black-or-indigenous-students
+</t>
+  </si>
+  <si>
+    <t>Dupont-Peppler Award for Black or Indigenous Students</t>
+  </si>
+  <si>
+    <t>One award, valued at up to $3,000, will be provided annually to a full-time Black or Indigenous undergraduate student enrolled in Year Three or Four of the Faculty of Arts or the Faculty of Engineering. For the purpose of this award, Black students may include African, Caribbean, Black Canadian, Afro-Latine, African American, or other African descent. For the purpose of this award, an Indigenous person is one who is a citizen or member of a First Nations community (Status/Non-Status), Métis or Inuit. To be eligible for consideration, students must be Canadian Citizens or Permanent Residents. Selection is based on academic achievement (minimum 75% cumulative average) and an essay describing the impact this award will have on their ability to pursue their educational goals. Preference will be given to students who are part of the first generation in their family to attend postsecondary education.  Interested students should submit an application by October 1. This fund is made possible by a donation from Ian (BASc ’94) and Donna (BA ’94) LeGrow. The award is named after the location of Ian and Donna’s first apartment together on the corner of Dupont and Peppler Streets in Waterloo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/e-launch-awards
+</t>
+  </si>
+  <si>
+    <t>E-Launch Awards</t>
+  </si>
+  <si>
+    <t>up to five awards, valued at $5,000 each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/engineering-award-peer-advocacy
+</t>
+  </si>
+  <si>
+    <t>Engineering Award for Peer Advocacy</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,200, will be provided annually to a full-time undergraduate student enrolled in Year Three or Four of any program in the Faculty of Engineering. Selection is based on academic achievement (minimum 75% cumulative average) combined with extracurricular involvement or participation in volunteer activities that help improve the student experience. Preference will be given to students who have been involved in initiatives related to mental health, student wellness, or the LGBTQ+ community. Interested students should submit an application by October 1. This fund is made possible by a donation from the Duqoum Family in memory of Natalie (Awn) Duqoum who was committed to improving the student experience on campus and making others feel welcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/engineering-society-leadership-excellence-award
+</t>
+  </si>
+  <si>
+    <t>Engineering Society Leadership Excellence Award</t>
+  </si>
+  <si>
+    <t>An award, valued at $1,000, is presented each term to a full-time undergraduate student enrolled in any term from 1B-4B of any Faculty of Engineering program who has displayed exceptional leadership within the University, Faculty of Engineering, or community at large. Candidates must have attained an average of 60% in their most recent academic term.  This award is supported by the University of Waterloo Engineering Society and the Office of the Dean of Engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/engineering-undergraduate-student-opportunity-award
+</t>
+  </si>
+  <si>
+    <t>Engineering Undergraduate Student Opportunity Award</t>
+  </si>
+  <si>
+    <t>Numerous awards are provided annually to support undergraduate students experiencing financial difficulties. The fund is made possible by donations from interested donors and by a matching grant from the province of Ontario. Eligible students must have resided in Ontario for 12 months prior to beginning their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/fiera-capital-corporation-award
+</t>
+  </si>
+  <si>
+    <t>Fiera Capital Corporation Award</t>
+  </si>
+  <si>
+    <t>Several awards, valued at a minimum of $500 each, are available to full-time undergraduate students experiencing financial difficulties and who have maintained a good academic record (75% minimum overall average).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/first-class-engineering-scholarships
+</t>
+  </si>
+  <si>
+    <t>First in Class Engineering Scholarships</t>
+  </si>
+  <si>
+    <t>Scholarships, valued at $500 each, are presented to the top student in each class based on performance in terms 1A to 4A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/foreign-student-bursary
+</t>
+  </si>
+  <si>
+    <t>Foreign Student Bursary</t>
+  </si>
+  <si>
+    <t>One bursary, valued at approximately $500, is provided annually to an undergraduate internatonal student experiencing financial difficulties. Complete the University of Waterloo Bursary form to be considered. This fund was established by the Committee for Emergency Relief for Foreign Students.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/fred-kelly-bursary
+</t>
+  </si>
+  <si>
+    <t>Fred Kelly Bursary</t>
+  </si>
+  <si>
+    <t>In memory of Fred Kelly, General Manager for the Federation of Students, the Federation has established a bursary fund. One bursary, valued at up to $1,000, may be awarded to a full-time undergraduate student who has a demonstrated financial need.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/george-and-cathy-raithby-award-entrepreneurship
+</t>
+  </si>
+  <si>
+    <t>George and Cathy Raithby Award for Entrepreneurship</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $2,800, will be provided annually to a full-time undergraduate student enrolled in Year Two, Three, or Four of any program in the Faculty of Engineering. Selection is based on academic achievement (minimum 70% cumulative average), combined with a demonstrated passion for entrepreneurship as evidenced through courses, business ideas, or completion of a business project. Preference will be given to candidates who can best demonstrate how their idea will positively impact Canada. Interested students should submit an application by October 1. This fund is made possible by a donation from George and Cathy Raithby to support entrepreneurial-minded engineering students in achieving their goals.</t>
+  </si>
+  <si>
+    <t>$2,800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ghd-foundation-engineering-bursary
+</t>
+  </si>
+  <si>
+    <t>GHD Foundation Engineering Bursary</t>
+  </si>
+  <si>
+    <t>A bursary, valued at $2,500, will be awarded annually to an undergraduate student enrolled in Year Three in the Faculty of Engineering who is from one of the following underrepresented groups: women students, Black students, or Indigenous students. Selection will be based on demonstrated financial need as determined by Waterloo. Candidates must have a minimum cumulative average of 75%. To be considered, students must complete the bursary application by the fall deadline. This fund is made possible by a donation from GHD Foundation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/hatch-scholarship
+</t>
+  </si>
+  <si>
+    <t>Hatch Scholarship</t>
+  </si>
+  <si>
+    <t>Up to three awards, valued at $4,000 each, will be awarded annually to full-time undergraduate students enrolled in Year Two, Three, or Four in Chemical, Civil, Computer, Electrical, Mechanical Engineering or Software Engineering on the basis of academic excellence (minimum 80% cumulative average), active participation/leadership in extracurricular or volunteer activities, interest in pursuing a consulting-type career, and strong communication skills.  Hatch may also offer the scholarship recipients consideration for a work-term position. Interested students should submit an application by October 1. Past recipients are eligible to apply in future years. This fund is made possible by a donation from Hatch, a leading global consulting, engineering, technologies, information systems, and project and construction management organization.</t>
+  </si>
+  <si>
+    <t>$4,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/howard-and-marita-boyd-scholarship
+</t>
+  </si>
+  <si>
+    <t>Howard and Marita Boyd Scholarship</t>
+  </si>
+  <si>
+    <t>Two scholarships, valued at $1,500 each, are awarded annually to full-time undergraduate students entering Year Two, Three, or Four in the Faculty of Mathematics and/or the Faculty of Engineering (excluding the School of Architecture) on the basis of academic excellence (minimum 80%) and demonstrated commitment to volunteerism.  Preference will be given to students who have been involved in Scouts Canada, Scottish Dance, or the Royal Canadian Air Force, Cadets or any other military service. Interested students should submit an application by October 1. This fund is made possible by a donation from Howard Boyd (BMath 1976) in memory of his wife Marita Boyd. Marita had a passion for volunteerism as shown through her service of over 40 years with Scouts Canada. She also loved all things Scottish, expressed through her active membership in the Royal Scottish Country Dance Society. In 2012 Marita was awarded the Queen’s Silver Jubilee medal by His Excellency the Right Honourable Governor General, David Johnston, for her commitment to community service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/husky-injection-molding-systems-ltd-student-opportunity-fund
+</t>
+  </si>
+  <si>
+    <t>Husky Injection Molding Systems Ltd. Student Opportunity Fund</t>
+  </si>
+  <si>
+    <t>Several awards, valued up to $2,000 each, have been established by Husky Injection Molding Systems Ltd. to assist full-time undergraduate students in the Faculty of Engineering who have a minimum 75% average and are experiencing financial difficulty. Preference will be given to students who have demonstrated leadership ability as evidenced by their involvement in extracurricular activities either at the University or in the community. Eligible students must have resided in Ontario for 12 months prior to the beginning of their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/indigenous-student-bursary
+</t>
+  </si>
+  <si>
+    <t>Indigenous Student Bursary</t>
+  </si>
+  <si>
+    <t>varies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ira-g-needles-memorial-bursary-fund
+</t>
+  </si>
+  <si>
+    <t>Ira G. Needles Memorial Bursary Fund</t>
+  </si>
+  <si>
+    <t>A bursary fund has been established in memory of Ira George Needles, one of the founding fathers of the University of Waterloo, Chairman of the Board of Governors from 1956 to 1966 when he was named Chancellor. Bursaries are awarded to full-time undergraduate students experiencing financial difficulties and who have maintained a 75% overall average.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/jg-hagey-alumni-bursary
+</t>
+  </si>
+  <si>
+    <t>J.G. Hagey Alumni Bursary</t>
+  </si>
+  <si>
+    <t>In memory of J.G. Hagey, President Emeritus of the University, and in recognition of his significant contributions to post-secondary education, the University of Waterloo Alumni has established a bursary fund. Several bursaries, to a maximum of $200 each, are awarded annually to students with financial need.</t>
+  </si>
+  <si>
+    <t>$200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/jain-family-award-entrepreneurship
+</t>
+  </si>
+  <si>
+    <t>Jain Family Award for Entrepreneurship</t>
+  </si>
+  <si>
+    <t>Two awards, valued at $5,000 each, will be provided annually to undergraduate or graduate students participating in Concept or Velocity programing at the University of Waterloo. Preference will be given to students pursuing this experience on a co-op term. Selection will be based on a merit-evaluation process including, but not limited to, the progress of the start-up’s business model and viability for commercial success. Interested students or teams should submit an application by October 31 to Velocity. This fund is made possible by a donation from the Vijay Anand Foundation to support student entrepreneurship at Waterloo and to encourage more students to follow their passion in the start-up community.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/janet-law-yip-memorial-award
+</t>
+  </si>
+  <si>
+    <t>Janet Law-Yip Memorial Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,300, will be provided annually to a full-time undergraduate student enrolled in Year Three or Four of any program in the Faculty of Engineering. Selection is based on academic achievement (minimum 75% cumulative average) combined with extracurricular involvement and/or volunteer activities. Preference will be given to students who have participated in student government. Interested students should submit an application by October 1. This fund is made possible by a donation from Janet Law-Yip’s family and friends in her memory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/jeffrey-aho-memorial-award
+</t>
+  </si>
+  <si>
+    <t>Jeffrey Aho Memorial Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,500, is provided annually to a full-time undergraduate student enrolled in Year Three or Four in any program in the Faculty of Engineering on the basis of academic achievement (minimum 75%) and extracurricular involvement in debating and/or student politics. Preference will be given to students who have participated in debating competitions or student government while attending the University of Waterloo. This fund is made possible by a donation from Linda and Brian Aho, to honour the memory of their son Jeffrey. As an undergraduate Engineering student, Jeffrey was an avid and successful debater who also contributed to campus life through involvement in student government.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/jerzy-w-anders-memorial-award
+</t>
+  </si>
+  <si>
+    <t>Jerzy W. Anders Memorial Award</t>
+  </si>
+  <si>
+    <t>An award, valued at approximately $250, has been established in memory of Jerzy Anders, a graduate of the University of Waterloo. The award is given to mature individuals who were forced to interrupt their university education due to financial difficulties or family obligations and are experiencing financial hardship upon re-entering the academic world. Mature students experiencing financial difficulties should include a letter detailing their circumstances along with the bursary application form.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/jim-kalbfleisch-award
+</t>
+  </si>
+  <si>
+    <t>Jim Kalbfleisch Award</t>
+  </si>
+  <si>
+    <t>Several awards, valued at $1,500 each, are provided annually to undergraduate students enrolled in Year Two, Three or Four of any program in any Faculty who have achieved a minimum overall average of 75% and who have demonstrated their involvement in student government at Waterloo.  This fund was established by Jim Kalbfleisch along with his friends and family in honour of his retirement, and further supported by gifts made in his memory after his passing in 2017.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/john-bergsma-award-engineering
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Bergsma Award in Engineering </t>
+  </si>
+  <si>
+    <t>An annual award, valued at approximately $1,000, has been established by Dr. John Bergsma for full-time undergraduate students in the Faculty of Engineering. To qualify, candidates must have a minimum overall average of 75% and demonstrate financial need. Preference will be given to students who have demonstrated leadership ability as evidenced by involvement in extracurricular activities at the University. Interested students should apply by the end of the first month of registration for each term. Eligible students must have resided in Ontario for 12 months prior to the beginning their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/jordan-banks-award
+</t>
+  </si>
+  <si>
+    <t>Jordan Banks Award</t>
+  </si>
+  <si>
+    <t>Up to two awards, valued at $2,500 each, are available annually for full-time undergraduate students enrolled in Year Two, Three, or Four of any program. Selection is based on a combination of academic achievement (minimum 75% cumulative average) and contributions to Jewish culture and community through extracurricular or volunteer activities on campus and/or in other communities. Interested students should submit an application by November 1. This fund is made possible by a donation from the Moses and Temara Tobe Foundation Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/jr-coutts-international-experience-awards
+</t>
+  </si>
+  <si>
+    <t>JR Coutts International Experience Awards</t>
+  </si>
+  <si>
+    <t>Several awards, valued at $1,500 to $2,500 each, are available each year to undergraduate students in any Faculty who wish to participate in an international experience including an academic exchange, a study term related to academic requirements, or a minimally-paid or volunteer work placement. These awards are intended to support students who are travelling to a country that they are not familiar with, thereby broadening their international experience. Selection is based on strong academic achievement (minimum 75% overall average), and on the nature and location of the experience. Award selection will take place once per term. Students must apply prior to the experience by one of the following pre-term deadlines: July 15, November 15, or March 15.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/kd-fryer-fass-award
+</t>
+  </si>
+  <si>
+    <t>K.D. Fryer – F.A.S.S. Award</t>
+  </si>
+  <si>
+    <t>A bursary fund has been established in memory of Kenneth D. Fryer, one of the founders and long time supporters of the F.A.S.S. theatre company. One bursary, valued at up to $500, is available for a full- or part-time student at any level in any program offered by the University of Waterloo. Candidates must have a minimum overall average of 60% and demonstrated financial need.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/karen-mark-scholarship
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karen Mark Scholarship </t>
+  </si>
+  <si>
+    <t>This $1,000 scholarship was established in 1989 by family and friends in memory of the late Karen Mark, a third-year Chemical Engineering student. The scholarship is awarded annually to a full-time undergraduate student who identifies as a woman enrolled in Year Three of a program in which women are underrepresented in the Faculty of Engineering. Selection is based on excellent academic achievement and demonstrated involvement and contributions to student life at Waterloo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/konrad-group-digital-innovation-scholarship
+</t>
+  </si>
+  <si>
+    <t>Konrad Group Digital Innovation Scholarship</t>
+  </si>
+  <si>
+    <t>A scholarship, valued at $2,000, will be provided annually to a full-time undergraduate student enrolled in Year Three or Four of Computer, Electrical, Management, Software, or Systems Design Engineering. Selection will be based on academic excellence (minimum 80% cumulative average) combined with a demonstrated interest in pursuing a career in digital technology through work-term experiences, extracurricular activities, and/or project work. Interested students should submit an online application by October 1. This fund is made possible by a donation from Konrad Group, a global digital consulting firm with services in strategy, design, and development.</t>
+  </si>
+  <si>
+    <t>$2,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/konrad-group-women-technology-scholarship-0
+</t>
+  </si>
+  <si>
+    <t>Konrad Group Women in Technology Scholarship</t>
+  </si>
+  <si>
+    <t>A scholarship, valued at $2,000, will be provided annually to a full-time undergraduate student who identifies as a woman enrolled in Year Three or Four of Computer, Electrical, Management, or Software Engineering wherein women are underrepresented. Selection is based on academic excellence (minimum 80% cumulative average) combined with a demonstrated interest in pursuing a career in digital technology through work-term experiences, extracurricular activities, and/or project work. Interested students should submit an online application by October 1. This fund is made possible by a donation from Konrad Group, a global digital consulting firm with services in strategy, design, and development.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/kothari-family-international-experience-award
+</t>
+  </si>
+  <si>
+    <t>Kothari Family International Experience Award</t>
+  </si>
+  <si>
+    <t>One award is provided annually to an undergraduate student enrolled in Year Two, Three or Four in the Faculty of Engineering who is participating in an international study or work experience, who has achieved a minimum overall average of 75% and who has a demonstrated financial need. Candidates must be Canadian citizens or permanent residents and have lived in Ontario for the entire 12-month period prior to beginning their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/kothari-family-upper-year-award
+</t>
+  </si>
+  <si>
+    <t>Kothari Family Upper-Year Award</t>
+  </si>
+  <si>
+    <t>One award, valued at $2,000, is awarded annually to an undergraduate student enrolled in Year Two, Three, or Four in the Faculty of Engineering, who has achieved a minimum overall average of 75% and who has a demonstrated financial need.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/liu-kennington-award-2slgbtq-engineering-community
+</t>
+  </si>
+  <si>
+    <t>Liu-Kennington Award for the 2SLGBTQ+ Engineering Community</t>
+  </si>
+  <si>
+    <t>An award, valued at $1,000, will be provided annually to a full-time undergraduate student enrolled in Year Two, Three, or Four in any program in the Faculty of Engineering. Selection is based on academic achievement (minimum 70% cumulative average) and positive contributions to the 2SLGBTQ+ community through extracurricular or volunteer involvement. Interested students should submit an on-line application by October 1. This fund is made possible by a donation from Michelle Liu and Allie Kennington to support and celebrate students of the 2SLGBTQ+ community within the Faculty of Engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/lovinsky-pierre-antoine-award
+</t>
+  </si>
+  <si>
+    <t>Lovinsky Pierre-Antoine Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,200, will be awarded annually to a full-time undergraduate student enrolled in Year Two, Three, or Four of any program. Selection will be based on a combination of academic achievement (minimum 70% cumulative average) and an essay (1000 words maximum) describing the demonstrable contributions they have made to the African, Caribbean, or Black communities within Canada through extracurricular or volunteer involvement. Interested students should submit an application by November 1. This fund is made possible by a generous donation from Briana C. Holmes, (BMath ’90) to honour friend Lovinsky Pierre-Antoine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/marga-i-weigel-engineering-international-exchange-award
+</t>
+  </si>
+  <si>
+    <t>Marga I. Weigel Engineering International Exchange Award</t>
+  </si>
+  <si>
+    <t>Up to four awards, valued at $2,500 each, will be available annually to full-time undergraduate students enrolled in Year Two, Three, or Four in any program in the Faculty of Engineering who are participating in an exchange program between UW and a partner institution in Germany or Austria or a low-paying co-op work term in Germany or Austria. Preference will be given to candidates pursuing an exchange program as well as to students who demonstrate financial need for the term(s) abroad. Candidates must have a minimum overall average of 75%. Upon their return, recipients are encouraged to provide a summary (1-2 page maximum) of their experience abroad to be shared with the donor and which may be published in an online journal to inspire other students to participate in an experiential endeavour in Germany or Austria. Interested applicants must complete the general International Experience Award application by July 15 or November 15. This fund is made possible by a donation from Dr. Marga Weigel, a proud UW alumna to encourage engineering students to pursue exchange opportunities in Germany or Austria, and to enhance their knowledge of European thought and culture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/mary-bland-engineering-award
+</t>
+  </si>
+  <si>
+    <t>Mary Bland Engineering Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,500, will be presented annually to a full-time undergraduate student enrolled in Year Two, Three, or Four of any program in the Faculty of Engineering. Selection will be based on academic achievement (minimum 75% cumulative average) combined with leadership involvement in Faculty of Engineering groups such as EngSoc, Engineering student design teams, WiE, and/or WEEF. Interested students should submit an application by October 1. This fund is made possible by the support of Waterloo Engineering faculty, staff, and alumni in honour of Mary Bland, former staff member of the Faculty of Engineering, to honour her commitment and support of engineering students during her 29-year career at the University of Waterloo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/mature-student-services-bursary
+</t>
+  </si>
+  <si>
+    <t>Mature Student Services Bursary</t>
+  </si>
+  <si>
+    <t>Mature undergraduate students who are studying on campus on a part-time basis and who are encountering financial difficulties are invited to apply. To be considered, applicants must be enrolled in a degree program and must be in good standing. Interested students should apply early in the term. This fund is made possible through the kind support of friends of the former Mature Student Services Office.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/mcneil-consumer-healthcare-paul-d-mitchell-bursary
+</t>
+  </si>
+  <si>
+    <t>McNeil Consumer Healthcare Paul D. Mitchell Bursary</t>
+  </si>
+  <si>
+    <t>Bursaries, valued at $1,000 each, have been established by McNeil Consumer Healthcare and by friends and colleagues of Paul D. Mitchell to assist students in financial need. Full-time undergraduates in any Faculty who are experiencing financial difficulties may apply. Eligible students must have resided in Ontario during the entire 12-month period immediately prior to beginning their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/metis-nation-ontario-bursary
+</t>
+  </si>
+  <si>
+    <t>Métis Nation of Ontario Bursary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/miklos-and-shanti-sandor-scholarship
+</t>
+  </si>
+  <si>
+    <t>Miklos and Shanti Sandor Scholarship</t>
+  </si>
+  <si>
+    <t>A scholarship, valued at up to $5,000, will be awarded annually to a full-time undergraduate student enrolled in Year Two, Three, or Four of any program the Faculty of Engineering (excluding the School of Architecture). Selection is based on academic excellence (minimum 80% cumulative average) combined with extracurricular or volunteer activities and a statement describing the impact this award will have on their ability to pursue their educational goals. Preference will be given to students who are part of the first generation in their family to attend post-secondary education. Interested students should submit an application by October 1. This scholarship was established by Ryan (BASc ’04 SYDE) and Patricia Sandor to celebrate his parents, Miklos and Shanti Sandor, who were immigrants and the first in their families to attend post-secondary education and whose dedication to earn UWaterloo degrees through distance education was an inspiration.</t>
+  </si>
+  <si>
+    <t>$5,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ncr-waterloo-student-opportunity-fund
+</t>
+  </si>
+  <si>
+    <t>NCR Waterloo Student Opportunity Fund</t>
+  </si>
+  <si>
+    <t>Several awards, valued at $1,000 each, have been established by NCR Waterloo to assist full-time undergraduate students with a minimum 78% overall average who are experiencing financial difficulty. Preference will be given to students who have demonstrated leadership ability as evidenced by involvement in extracurricular activities either at the University or within the community. Eligible students must have resided in Ontario for 12 months prior to the beginning of their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/nitin-jain-family-award-entrepreneurship
+</t>
+  </si>
+  <si>
+    <t>Nitin Jain Family Award for Entrepreneurship</t>
+  </si>
+  <si>
+    <t>One award, valued at $5,000, will be provided annually to undergraduate or graduate students participating in Concept or Velocity programing at the University of Waterloo. Preference will be given to students pursuing this experience on a co-op term. Selection will be based on a merit-evaluation process including, but not limited to, the progress of the start-up’s business model and viability for commercial success. Interested students or teams should submit an application by the Friday of the second week of the Fall term to Velocity. This fund is made possible by a donation from proud UW alumnus Nitin Jain (BASc ’01) and the Vijay Anand Foundation to support student entrepreneurship at Waterloo and to encourage more students to follow their passion in the start-up community.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/nserc-undergraduate-research-awards
+</t>
+  </si>
+  <si>
+    <t>NSERC Undergraduate Research Awards</t>
+  </si>
+  <si>
+    <t>Natural Sciences and Engineering Research Council of Canada (NSERC) rewards excellence and nurtures Canada's brightest young minds by funding top science and engineering students in Canada's post-secondary institutions. NSERC Undergraduate Research Awards enable the recipient to gain research experience by working full time with an NSERC grant holder on a research project in a university laboratory. These awards have a value of $6,000 (plus a required USRA top-up) and students are normally expected to work 35 hours per week for 16 consecutive weeks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ontario-first-generation-bursary
+</t>
+  </si>
+  <si>
+    <t>Ontario First Generation Bursary</t>
+  </si>
+  <si>
+    <t>Several bursaries, of varying value, are awarded to full- or part-time undergraduate students with financial need who are the first in their family to attend post-secondary education (i.e., parent(s) have never participated in post-secondary studies anywhere in the world on either a full- or part-time basis). Candidates must be Ontario residents and be enrolled in a first-entry undergraduate program; second entry programs (e.g., Pharmacy or Optometry) and graduate programs are not eligible. Note: you are not required to apply for OSAP to be considered for this bursary. Interested students must complete the University of Waterloo Bursary application.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ontario-power-generation-power-achieve-award
+</t>
+  </si>
+  <si>
+    <t>Ontario Power Generation Power to Achieve Award</t>
+  </si>
+  <si>
+    <t>Two awards, valued at $2,500 each, will be provided annually to full-time undergraduate students enrolled in Year Two, Three or Four in any program in the Faculty of Engineering who are from one of the following underrepresented groups: women enrolled in an engineering program wherein women are underrepresented, Black students, Indigenous students, students living with a disability. Selection is based on academic achievement (minimum 75% cumulative average) combined with positive contributions made to their school and/or community. Interested students should submit an application explaining how they meet the criteria of the award by October 1. This fund is made possible by a donation from Ontario Power Generation to support the next generation of engineers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ontario-professional-engineers-foundation-education
+</t>
+  </si>
+  <si>
+    <t>Ontario Professional Engineers Foundation for Education Undergraduate Scholarship</t>
+  </si>
+  <si>
+    <t>Eight scholarships, valued at $1,500 each, will be provided annually to full-time undergraduate students enrolled in CEAB-Accredited programs in the Faculty of Engineering including Software Engineering. At least four of the scholarships will be provided to students who identify as women enrolled in an Engineering program in which women are underrepresented. These scholarships will recognize outstanding students entering each of the 2A, 3A, 4A and 4B study terms. Selection will be based on academic achievement (minimum 80% cumulative average), demonstrated leadership through participation in professional affairs, volunteer and/or extracurricular activities. Students may also include a statement describing the impact this award will have on their ability to pursue their educational goals. Interested students should submit an online application as well as a current resume during the 1B, 2B, 3B, and 4B terms. This fund is made possible by a donation from Ontario Professional Engineers Foundation for Education to acknowledge the hard work of engineering students and promote the relevancy of becoming a licensed Professional Engineer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ottawa-university-waterloo-alumni-bursary
+</t>
+  </si>
+  <si>
+    <t>Ottawa-University of Waterloo Alumni Bursary</t>
+  </si>
+  <si>
+    <t>One or more bursaries, valued at a minimum of $500 each, are available to full-time undergraduate students enrolled in first-, second-, third-, or fourth-year in any Faculty who have a financial need and a minimum overall average of 65%. Eligible students must have a home address in the Ottawa area, including the counties of Frontenac, Ottawa-Carleton, Prescott &amp; Russell, and Renfrew. This fund has been established and is supported by University of Waterloo alumni residing in the Ottawa area.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/overbeeke-family-entrepreneurship-excellence-award
+</t>
+  </si>
+  <si>
+    <t>Overbeeke Family Entrepreneurship Excellence Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $10,000, will be awarded each term to a full-time undergraduate student enrolled in any year in the Faculty of Engineering who is pursuing an Enterprise Co-op opportunity. Selection will be based on the development of an outstanding presentation, business plan review, clarity of business description, and preparedness to lead a venture or social enterprise. Interested students should apply to be accepted into the Enterprise Co-op program no later than the start of the co-op term. This fund is made possible by a donation from H. David Overbeeke (BASc ’85, Mechanical Engineering) to support engineering students with their entrepreneurial goals and business education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/paul-berg-memorial-award
+</t>
+  </si>
+  <si>
+    <t>Paul Berg Memorial Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $500, may be provided annually to an undergraduate student in second-year or above who demonstrates their involvement in extracurricular music activities on campus and who has attained at least a 75% average during the most recently preceding term of studies. This award is made possible by the friends of Paul Berg, Director of the University Centre of the Arts, 1960-1975, and conductor of the Schneider Male Chorus, 1942-1975.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/professional-development-prize-project-management
+</t>
+  </si>
+  <si>
+    <t>Professional Development Prize in Project Management</t>
+  </si>
+  <si>
+    <t>Three book prizes are awarded each term to the students who have achieved the highest overall course grade in the PD 5: Project Management course and who have also successfully completed the Certified Associate in Project Management (CAPM) Mock Exam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/professor-t-prasad-award
+</t>
+  </si>
+  <si>
+    <t>Professor T. Prasad Memorial Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,500, is presented annually to a deserving undergraduate student enrolled in any program in the Faculty of Engineering who has demonstrated a new direction in her/his academic efforts as evidenced by an increase in term average from 2B to 3A. This award is in remembrance of Professor Tribhuan Prasad (1924-1993), whose love of teaching helped many students reach their full potential. This fund is made possible through the generosity of Professor T. Prasad’s family and friends, students and colleagues in grateful memory of an exceptional teacher and distinguished professor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/r-bruce-dymond-memorial-bursary
+</t>
+  </si>
+  <si>
+    <t>R. Bruce Dymond Memorial Bursary</t>
+  </si>
+  <si>
+    <t>A bursary fund has been established in memory of R. Bruce Dymond to assist students in the Faculty of Engineering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/raymond-legge-engineering-pride-award
+</t>
+  </si>
+  <si>
+    <t>Raymond L. Legge Engineering Pride Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,500, will be provided annually to an undergraduate student enrolled in Year Two, Three or Four of any program in the Faculty of Engineering, with preference to Chemical Engineering. Selection will be based on academic achievement (minimum 70% cumulative average) and positive contributions to the 2SLGBTQ+ community demonstrated through extracurricular involvement and/or volunteer activities. Interested students should submit an application by October 1. This award was established in memory of Distinguished Professor Emeritus Raymond L. Legge for his significant contributions to the University of Waterloo and Chemical Engineering community. The award is aimed at helping exceptional engineering undergraduates who contribute to the 2SLGBTQ+ community.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ron-eydt-travel-award
+</t>
+  </si>
+  <si>
+    <t>Ron Eydt Travel Award</t>
+  </si>
+  <si>
+    <t>Undergraduate students who participate in one of the approved full-time exchange programs between the University of Waterloo and other universities may be eligible for financial assistance through this fund. Students must have demonstrated University of Waterloo student leadership and campus involvement, have maintained a minimum B overall average, and must demonstrate financial need. Candidates must be Canadian citizens or permanent residents and have lived in Ontario for the entire 12-month period prior to beginning their post-secondary education.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/ross-doris-dixon-bursary-students-disabilities
+</t>
+  </si>
+  <si>
+    <t>Ross &amp; Doris Dixon Bursary for Students with Disabilities</t>
+  </si>
+  <si>
+    <t>One or more bursaries, valued up to $2,000, are awarded annually to students with disabilities who are experiencing financial difficulties and are studying on a full- or part-time basis in a degree status or non-degree status program. A minimum overall academic average of 60% is required. Applicants should explain their eligibility for assistance from this source and/or indicate if they have documentation on file at AccessAbility Services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sameer-ahuja-perseverance-award
+</t>
+  </si>
+  <si>
+    <t>Sameer Ahuja Perseverance Award</t>
+  </si>
+  <si>
+    <t>This award has been established by family members in honour of Sameer Ahuja (1980-2004) to recognize and provide financial assistance to students who are persevering to obtain a degree while facing the challenges of a life threatening illness and/or a physical disability. Sameer was an exceptional young man who was determined to persevere with his studies despite a life threatening illness which created numerous physical challenges for him. He was a true champion for equal access opportunities. Sameer will always be remembered for his courage, determination, positive attitude, and the ability to keep his humor alive during the most difficult time of his life. Interested undergraduate students in any Faculty who have obtained a minimum overall average of 65% while facing the challenges of a life threatening illness and/or a physical disability, and who have a demonstrated financial need, are invited to submit an application. Awards vary in value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sandford-fleming-foundation-sff-award-teaching-assistantship
+</t>
+  </si>
+  <si>
+    <t>Sandford Fleming Foundation (SFF) Award for Teaching Assistantship Excellence</t>
+  </si>
+  <si>
+    <t>one award, valued at $500, is made annually in each academic department and in first year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sandford-fleming-foundation-sff-debate-awards
+</t>
+  </si>
+  <si>
+    <t>Sandford Fleming Foundation (SFF) Debate Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awards available are as follows: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sandford-fleming-foundation-sff-innovative-design
+</t>
+  </si>
+  <si>
+    <t>Sandford Fleming Foundation (SFF) Innovative Design Competition Award</t>
+  </si>
+  <si>
+    <t>Two team awards valued at $800 ($200 per student assuming a team of 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sandford-fleming-foundation-sff-memorial-leadership-award
+</t>
+  </si>
+  <si>
+    <t>Sandford Fleming Foundation (SFF) Memorial Leadership Award</t>
+  </si>
+  <si>
+    <t>One award is available and consists of:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sandford-fleming-foundation-sff-technical-speaker
+</t>
+  </si>
+  <si>
+    <t>Sandford Fleming Foundation (SFF) Technical Speaker Competition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Technical Speaker competition was established to encourage public speaking skills within the student body. The competition is held each term. Six presenters are chosen from submitted abstracts. The winner will receive an award of $400, second place receiving $200, and third place receiving $75. The other participants receive $25 each. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sandford-fleming-foundation-sff-undergraduate-travel-grants
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandford Fleming Foundation (SFF) Undergraduate Travel Grants </t>
+  </si>
+  <si>
+    <t>These awards were initiated to assist in the support of students presenting scholarly papers at academic conferences. It was the original intent that these would be used for travel for which other support did not exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/shah-family-engineering-bursary
+</t>
+  </si>
+  <si>
+    <t>Shah Family Engineering Bursary</t>
+  </si>
+  <si>
+    <t>Several bursaries, valued at up to $5,000 each, will be provided annually to full-time undergraduate students enrolled in Year Two, Three, or Four of any program in the Faculty of Engineering. Selection is based on academic excellence (minimum 80% cumulative average) and demonstrated financial need. To be considered, students must complete the University of Waterloo bursary application by the fall or winter bursary deadline. This fund is made possible by Kris Shah (BASc ’86, Electrical Engineering) to remove financial barriers and invest in the future generation of engineering talent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/shamoun-sufer-memorial-engineering-award
+</t>
+  </si>
+  <si>
+    <t>Shamoun Sufer Memorial Engineering Award</t>
+  </si>
+  <si>
+    <t>An award, valued at $1,000, will be awarded annually to a full-time undergraduate student enrolled in Year Two, Three, Four in the Faculty of Engineering who has a minimum overall average of 75% and a demonstrated financial need. This fund is made possible by donations from Davin Sufer who established this award in loving memory of his father, Shamoun Sufer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/siemens-computer-engineering-award
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens Computer Engineering Award </t>
+  </si>
+  <si>
+    <t>Two awards, valued at $5,000 each, will be provided to students enrolled in Year Three of the Computer Engineering program in the Faculty of Engineering. One award is reserved for a student who identifies as a woman to address the historic and current underrepresentation of women in Computer Engineering. Selection will be based on academic achievement (minimum 75% cumulative average), combined with extracurricular involvement, and a statement describing the impact this award will have on their ability to pursue their educational goals. Interested students should submit an on-line application by October 1st. This award is made possible by a donation from co-op employer, Siemens Canada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/special-achievement-bursary-students-disabilities
+</t>
+  </si>
+  <si>
+    <t>Special Achievement Bursary for Students with Disabilities</t>
+  </si>
+  <si>
+    <t>One bursary, valued at up to $1,000, may be awarded to an undergraduate student who is studying on a full- or part-time basis. Applicants should include a letter to explain their eligibility for assistance from this source and attach appropriate documentation outlining their disability or indicate that they have documentation on file at AccessAbility Services.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/stella-margaret-callfas-bursary
+</t>
+  </si>
+  <si>
+    <t>Stella Margaret Callfas Bursary</t>
+  </si>
+  <si>
+    <t>Bursaries, of varying amounts, are available to undergraduate and graduate students who are experiencing financial difficulty as a result of the responsibilities associated with being a sole-support parent, with preference to students who identify as women. Interested full- or part-time students enrolled in Year One or above who are studying towards a degree or diploma and who have a minimum overall average of 72% or above may apply. This bursary is made possible by a gift from William F. Goetz in memory of his mother, Stella Margaret Callfas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/student-life-centre-management-board-bursary
+</t>
+  </si>
+  <si>
+    <t>Student Life Centre Management Board Bursary</t>
+  </si>
+  <si>
+    <t>A bursary fund established by the Student Life Centre Management Board (formerly Campus Centre Board) is available to graduate and undergraduate students experiencing financial difficulties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/sundance-indigenous-award
+</t>
+  </si>
+  <si>
+    <t>SUNDANCe Indigenous Award</t>
+  </si>
+  <si>
+    <t>An award, valued at up to $1,500, is available annually for an Indigenous undergraduate student enrolled in full-time degree studies in any year of any program at the University of Waterloo, Renison University College or St. Jerome’s University. To be eligible, students must have completed the Indigenous Verification section in Quest and have had their Indigenous identity verified by the Office of Indigenous Relations at the University of Waterloo. Candidacy is limited to Ontario residents. Selection will be based on demonstrated connection and/or contributions to Indigenous communities through extracurricular and/or volunteer activities combined with financial need. As part of the application statement, students are asked to describe what receiving this award would mean in achieving their educational goals and covering expenses. Interested students should complete the Fall General Award Application by November 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/tikkun-olam-award
+</t>
+  </si>
+  <si>
+    <t>Tikkun Olam Award</t>
+  </si>
+  <si>
+    <t>One award, valued at $2,000, will be provided annually to a full-time undergraduate or graduate student enrolled in any year of any program at the University of Waterloo. Selection will be based on academic achievement (minimum 70% cumulative average) combined with contributions to Jewish culture and community through extracurricular or volunteer activities on campus and/or in other communities. As part of their application, students must include an essay/statement of 250-1,000 words to describe these contributions. Interested students should submit an application by November 1. This award has been established by Maryam Latifpoor-Keparoutis, along with family and friends, to inspire, encourage and support students at the University of Waterloo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-25th-anniversary-bursary
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo 25th Anniversary Bursary</t>
+  </si>
+  <si>
+    <t>This fund was established by the University from the sale of anniversary souvenirs in the Bookstore, along with proceeds from many anniversary events in recognition of the 25th anniversary of the University of Waterloo. A bursary, valued at approximately $1,000, is awarded to a full-time undergraduate student in any Faculty who is in need of financial assistance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-50th-anniversary-undergraduate
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo 50th Anniversary Undergraduate Scholarship</t>
+  </si>
+  <si>
+    <t>several scholarships valued at up to varying values are available annually</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-bursary-fund
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo Bursary Fund</t>
+  </si>
+  <si>
+    <t>The University has established a bursary endowment fund to assist students with demonstrated financial need. Bursaries, of varying values, are awarded to full- or part-time undergraduate students in any faculty of the University.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-extended-society-care-bursary
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo Extended Society Care Bursary</t>
+  </si>
+  <si>
+    <t>Bursaries, of varying amounts, are available for eligible students to assist with their educational costs. To be considered, students must be receiving OSAP in the current academic year, have self-identified on the OSAP application as currently being in extended society care in Ontario (previously called Crown ward) or in receipt of the extended care and maintenance allowance, and be registered in either part-time or full-time studies. Interested students may apply using the UW Bursary application on Quest and specifying that they wish to be considered for the Extended Society Care Bursary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-international-experience-awards
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo International Experience Awards</t>
+  </si>
+  <si>
+    <t>Several awards, valued at up to $2,500 each, are available annually to full-time undergraduate and graduate students who participate in an international experience, including a minimally-paid or volunteer international co-op work placement, a volunteer placement, an academic exchange or a study term related to academic requirements. Students in any Faculty, in satisfactory academic standing, who are planning to participate in an international experience are eligible to apply. Preference will be given to students with financial need who will be travelling to an unfamiliar country where they will experience a different culture in a new learning environment.  Award selection will take place once per term. Students should apply as soon as they are able to confirm the details of their intended experience by one of the applicable term deadlines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-retirees-award
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo Retirees' Award</t>
+  </si>
+  <si>
+    <t>The University of Waterloo Retirees' Association has established this fund to assist students with demonstrated financial need. Several bursaries, valued at up to $1,000 each, are provided to full- or part-time undergraduate and graduate students enrolled in any program at the University.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-staff-association-award
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo Staff Association Award</t>
+  </si>
+  <si>
+    <t>Several awards, valued at $500 - $1,000 each, are provided annually to full- or part-time undergraduate or graduate students enrolled in a degree program at the University of Waterloo who are affiliated with the UW Staff Association (UWSA) as a member or as the child, spouse, grandchild, or dependent of a current UWSA member. Award selection will be based on academic merit (minimum 70% cumulative average) combined with contributions to the University or the community through extracurricular or volunteer activities. Applications are due annually by November 15. Awards of $1,000 will be provided to recipients who qualify for the tuition benefit of 50% (per Policy 24) or for those who do not qualify for this benefit at all. Awards of $500 will be provided to recipients who qualify for a tuition benefit of 100% (per Policy 4). This award is supported by the University of Waterloo Staff Association.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/university-waterloo-undergraduate-student-opportunity-award
+</t>
+  </si>
+  <si>
+    <t>University of Waterloo Undergraduate Student Opportunity Award</t>
+  </si>
+  <si>
+    <t>Several awards are provided annually to support academically qualified students experiencing financial difficulties. Eligible students must have resided in Ontario for 12 months prior to the beginning of their post-secondary education. This fund is made possible by donations from interested donors and by a matching grant from the Province of Ontario. In addition to a large number of general donations, contributions have been received from: The Atkinson Charitable Foundation, The Gary Buckley Memorial Fund, The Chawkers Foundation, and the Helen Pollock Bursary Fund.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/waterloo-undergraduate-student-association-wusa-bursary
+</t>
+  </si>
+  <si>
+    <t>Waterloo Undergraduate Student Association (WUSA) Bursary</t>
+  </si>
+  <si>
+    <t>One bursary, valued at approximately $500, is awarded annually to a full-time undergraduate student experiencing financial difficulties, maintaining a 75% overall average, and who is active in campus student organizations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/wescast-industries-continuous-learning-award
+</t>
+  </si>
+  <si>
+    <t>Wescast Industries Continuous Learning Award</t>
+  </si>
+  <si>
+    <t>An annual award, valued at $1,000, has been established by Wescast Industries Ltd., to recognize academic performance and financial need among students in Accounting and Engineering. To be eligible, candidates must have maintained a 75% minimum average.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/women-engineering-bursary
+</t>
+  </si>
+  <si>
+    <t>Women in Engineering Bursary</t>
+  </si>
+  <si>
+    <t>A bursary, valued at $2,000, will be awarded annually to a full-time undergraduate student who identifies as a woman enrolled in Year Two, Three, or Four of any program in the Faculty of Engineering wherein women are underrepresented, who has a demonstrated financial need. To be considered, students must complete a bursary application by the fall term bursary deadline. This fund was created by Alistair Baker to support women in the Faculty of Engineering who need financial support.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://uwaterloo.ca/student-awards-financial-aid/awards/wusa-advocacy-awards
+</t>
+  </si>
+  <si>
+    <t>WUSA Advocacy Awards</t>
+  </si>
+  <si>
+    <t>Awards valued at $1,000 each, are awarded annually to full-time undergraduate students enrolled at the University of Waterloo who have made meaningful contributions through extracurricular activities associated with the Waterloo Undergraduate Student Association (excluding paid positions). Preference will be given to students who have been involved in activities related to mental health, equity, student wellness and all other advocacy initiatives. Interested students should submit an application by November 1st. This fund is made possible by a gift from the Federation of Students, operating as the Waterloo Undergraduate Student Association (WUSA).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,13 +1234,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -363,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="28.5703125" customWidth="1"/>
@@ -389,7 +1565,1830 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" t="s">
+        <v>117</v>
+      </c>
+      <c r="F36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" t="s">
+        <v>126</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+      <c r="F40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" t="s">
+        <v>132</v>
+      </c>
+      <c r="E41" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" t="s">
+        <v>135</v>
+      </c>
+      <c r="F42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" t="s">
+        <v>149</v>
+      </c>
+      <c r="E46" t="s">
+        <v>63</v>
+      </c>
+      <c r="F46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="s">
+        <v>152</v>
+      </c>
+      <c r="F47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" t="s">
+        <v>155</v>
+      </c>
+      <c r="F48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" t="s">
+        <v>158</v>
+      </c>
+      <c r="F49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" t="s">
+        <v>162</v>
+      </c>
+      <c r="F50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+      <c r="F51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" t="s">
+        <v>171</v>
+      </c>
+      <c r="F53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" t="s">
+        <v>177</v>
+      </c>
+      <c r="F55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" t="s">
+        <v>180</v>
+      </c>
+      <c r="F56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" t="s">
+        <v>186</v>
+      </c>
+      <c r="F58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B59" t="s">
+        <v>188</v>
+      </c>
+      <c r="C59" t="s">
+        <v>189</v>
+      </c>
+      <c r="F59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B60" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" t="s">
+        <v>196</v>
+      </c>
+      <c r="F61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B62" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" t="s">
+        <v>199</v>
+      </c>
+      <c r="E62" t="s">
+        <v>196</v>
+      </c>
+      <c r="F62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" t="s">
+        <v>201</v>
+      </c>
+      <c r="C63" t="s">
+        <v>202</v>
+      </c>
+      <c r="E63" t="s">
+        <v>196</v>
+      </c>
+      <c r="F63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B64" t="s">
+        <v>204</v>
+      </c>
+      <c r="C64" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64" t="s">
+        <v>196</v>
+      </c>
+      <c r="F64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B65" t="s">
+        <v>207</v>
+      </c>
+      <c r="C65" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B66" t="s">
+        <v>210</v>
+      </c>
+      <c r="C66" t="s">
+        <v>211</v>
+      </c>
+      <c r="F66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B67" t="s">
+        <v>213</v>
+      </c>
+      <c r="C67" t="s">
+        <v>214</v>
+      </c>
+      <c r="E67" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B68" t="s">
+        <v>216</v>
+      </c>
+      <c r="C68" t="s">
+        <v>217</v>
+      </c>
+      <c r="F68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" t="s">
+        <v>219</v>
+      </c>
+      <c r="C69" t="s">
+        <v>220</v>
+      </c>
+      <c r="F69" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B70" t="s">
+        <v>222</v>
+      </c>
+      <c r="C70" t="s">
+        <v>223</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B71" t="s">
+        <v>225</v>
+      </c>
+      <c r="C71" t="s">
+        <v>155</v>
+      </c>
+      <c r="F71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B72" t="s">
+        <v>227</v>
+      </c>
+      <c r="C72" t="s">
+        <v>228</v>
+      </c>
+      <c r="E72" t="s">
+        <v>229</v>
+      </c>
+      <c r="F72" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B73" t="s">
+        <v>231</v>
+      </c>
+      <c r="C73" t="s">
+        <v>232</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B74" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" t="s">
+        <v>235</v>
+      </c>
+      <c r="E74" t="s">
+        <v>229</v>
+      </c>
+      <c r="F74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B75" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" t="s">
+        <v>238</v>
+      </c>
+      <c r="F75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B76" t="s">
+        <v>240</v>
+      </c>
+      <c r="C76" t="s">
+        <v>241</v>
+      </c>
+      <c r="F76" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B77" t="s">
+        <v>243</v>
+      </c>
+      <c r="C77" t="s">
+        <v>244</v>
+      </c>
+      <c r="E77" t="s">
+        <v>40</v>
+      </c>
+      <c r="F77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B78" t="s">
+        <v>246</v>
+      </c>
+      <c r="C78" t="s">
+        <v>247</v>
+      </c>
+      <c r="E78" t="s">
+        <v>63</v>
+      </c>
+      <c r="F78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B79" t="s">
+        <v>249</v>
+      </c>
+      <c r="C79" t="s">
+        <v>250</v>
+      </c>
+      <c r="F79" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B80" t="s">
+        <v>252</v>
+      </c>
+      <c r="C80" t="s">
+        <v>253</v>
+      </c>
+      <c r="F80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B81" t="s">
+        <v>255</v>
+      </c>
+      <c r="C81" t="s">
+        <v>256</v>
+      </c>
+      <c r="F81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B82" t="s">
+        <v>258</v>
+      </c>
+      <c r="C82" t="s">
+        <v>259</v>
+      </c>
+      <c r="F82" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B83" t="s">
+        <v>261</v>
+      </c>
+      <c r="C83" t="s">
+        <v>262</v>
+      </c>
+      <c r="F83" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B84" t="s">
+        <v>264</v>
+      </c>
+      <c r="C84" t="s">
+        <v>265</v>
+      </c>
+      <c r="F84" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B85" t="s">
+        <v>267</v>
+      </c>
+      <c r="C85" t="s">
+        <v>268</v>
+      </c>
+      <c r="F85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B86" t="s">
+        <v>270</v>
+      </c>
+      <c r="C86" t="s">
+        <v>271</v>
+      </c>
+      <c r="F86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B87" t="s">
+        <v>273</v>
+      </c>
+      <c r="C87" t="s">
+        <v>274</v>
+      </c>
+      <c r="F87" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B88" t="s">
+        <v>276</v>
+      </c>
+      <c r="C88" t="s">
+        <v>277</v>
+      </c>
+      <c r="F88" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B89" t="s">
+        <v>279</v>
+      </c>
+      <c r="C89" t="s">
+        <v>280</v>
+      </c>
+      <c r="F89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B90" t="s">
+        <v>282</v>
+      </c>
+      <c r="C90" t="s">
+        <v>283</v>
+      </c>
+      <c r="F90" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B91" t="s">
+        <v>285</v>
+      </c>
+      <c r="C91" t="s">
+        <v>286</v>
+      </c>
+      <c r="F91" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B92" t="s">
+        <v>288</v>
+      </c>
+      <c r="C92" t="s">
+        <v>289</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B93" t="s">
+        <v>291</v>
+      </c>
+      <c r="C93" t="s">
+        <v>292</v>
+      </c>
+      <c r="F93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B94" t="s">
+        <v>294</v>
+      </c>
+      <c r="C94" t="s">
+        <v>295</v>
+      </c>
+      <c r="F94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B95" t="s">
+        <v>297</v>
+      </c>
+      <c r="C95" t="s">
+        <v>298</v>
+      </c>
+      <c r="F95" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B96" t="s">
+        <v>300</v>
+      </c>
+      <c r="C96" t="s">
+        <v>301</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B97" t="s">
+        <v>303</v>
+      </c>
+      <c r="C97" t="s">
+        <v>304</v>
+      </c>
+      <c r="E97" t="s">
+        <v>229</v>
+      </c>
+      <c r="F97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B98" t="s">
+        <v>306</v>
+      </c>
+      <c r="C98" t="s">
+        <v>307</v>
+      </c>
+      <c r="F98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B99" t="s">
+        <v>309</v>
+      </c>
+      <c r="C99" t="s">
+        <v>310</v>
+      </c>
+      <c r="F99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B100" t="s">
+        <v>312</v>
+      </c>
+      <c r="C100" t="s">
+        <v>313</v>
+      </c>
+      <c r="F100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B101" t="s">
+        <v>315</v>
+      </c>
+      <c r="C101" t="s">
+        <v>316</v>
+      </c>
+      <c r="E101" t="s">
+        <v>63</v>
+      </c>
+      <c r="F101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B102" t="s">
+        <v>318</v>
+      </c>
+      <c r="C102" t="s">
+        <v>319</v>
+      </c>
+      <c r="E102" t="s">
+        <v>196</v>
+      </c>
+      <c r="F102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B103" t="s">
+        <v>321</v>
+      </c>
+      <c r="C103" t="s">
+        <v>322</v>
+      </c>
+      <c r="F103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B104" t="s">
+        <v>324</v>
+      </c>
+      <c r="C104" t="s">
+        <v>325</v>
+      </c>
+      <c r="F104" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B105" t="s">
+        <v>327</v>
+      </c>
+      <c r="C105" t="s">
+        <v>328</v>
+      </c>
+      <c r="F105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B106" t="s">
+        <v>330</v>
+      </c>
+      <c r="C106" t="s">
+        <v>331</v>
+      </c>
+      <c r="F106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B107" t="s">
+        <v>333</v>
+      </c>
+      <c r="C107" t="s">
+        <v>334</v>
+      </c>
+      <c r="F107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B108" t="s">
+        <v>336</v>
+      </c>
+      <c r="C108" t="s">
+        <v>337</v>
+      </c>
+      <c r="F108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B109" t="s">
+        <v>339</v>
+      </c>
+      <c r="C109" t="s">
+        <v>340</v>
+      </c>
+      <c r="F109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B110" t="s">
+        <v>342</v>
+      </c>
+      <c r="C110" t="s">
+        <v>343</v>
+      </c>
+      <c r="F110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B111" t="s">
+        <v>345</v>
+      </c>
+      <c r="C111" t="s">
+        <v>346</v>
+      </c>
+      <c r="F111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B112" t="s">
+        <v>348</v>
+      </c>
+      <c r="C112" t="s">
+        <v>349</v>
+      </c>
+      <c r="E112" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B113" t="s">
+        <v>351</v>
+      </c>
+      <c r="C113" t="s">
+        <v>352</v>
+      </c>
+      <c r="E113" t="s">
+        <v>196</v>
+      </c>
+      <c r="F113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B114" t="s">
+        <v>354</v>
+      </c>
+      <c r="C114" t="s">
+        <v>355</v>
+      </c>
+      <c r="E114" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5"/>
+    <hyperlink ref="A7" r:id="rId6"/>
+    <hyperlink ref="A8" r:id="rId7"/>
+    <hyperlink ref="A9" r:id="rId8"/>
+    <hyperlink ref="A10" r:id="rId9"/>
+    <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+    <hyperlink ref="A41" r:id="rId40"/>
+    <hyperlink ref="A42" r:id="rId41"/>
+    <hyperlink ref="A43" r:id="rId42"/>
+    <hyperlink ref="A44" r:id="rId43"/>
+    <hyperlink ref="A45" r:id="rId44"/>
+    <hyperlink ref="A46" r:id="rId45"/>
+    <hyperlink ref="A47" r:id="rId46"/>
+    <hyperlink ref="A48" r:id="rId47"/>
+    <hyperlink ref="A49" r:id="rId48"/>
+    <hyperlink ref="A50" r:id="rId49"/>
+    <hyperlink ref="A51" r:id="rId50"/>
+    <hyperlink ref="A52" r:id="rId51"/>
+    <hyperlink ref="A53" r:id="rId52"/>
+    <hyperlink ref="A54" r:id="rId53"/>
+    <hyperlink ref="A55" r:id="rId54"/>
+    <hyperlink ref="A56" r:id="rId55"/>
+    <hyperlink ref="A57" r:id="rId56"/>
+    <hyperlink ref="A58" r:id="rId57"/>
+    <hyperlink ref="A59" r:id="rId58"/>
+    <hyperlink ref="A60" r:id="rId59"/>
+    <hyperlink ref="A61" r:id="rId60"/>
+    <hyperlink ref="A62" r:id="rId61"/>
+    <hyperlink ref="A63" r:id="rId62"/>
+    <hyperlink ref="A64" r:id="rId63"/>
+    <hyperlink ref="A65" r:id="rId64"/>
+    <hyperlink ref="A66" r:id="rId65"/>
+    <hyperlink ref="A67" r:id="rId66"/>
+    <hyperlink ref="A68" r:id="rId67"/>
+    <hyperlink ref="A69" r:id="rId68"/>
+    <hyperlink ref="A70" r:id="rId69"/>
+    <hyperlink ref="A71" r:id="rId70"/>
+    <hyperlink ref="A72" r:id="rId71"/>
+    <hyperlink ref="A73" r:id="rId72"/>
+    <hyperlink ref="A74" r:id="rId73"/>
+    <hyperlink ref="A75" r:id="rId74"/>
+    <hyperlink ref="A76" r:id="rId75"/>
+    <hyperlink ref="A77" r:id="rId76"/>
+    <hyperlink ref="A78" r:id="rId77"/>
+    <hyperlink ref="A79" r:id="rId78"/>
+    <hyperlink ref="A80" r:id="rId79"/>
+    <hyperlink ref="A81" r:id="rId80"/>
+    <hyperlink ref="A82" r:id="rId81"/>
+    <hyperlink ref="A83" r:id="rId82"/>
+    <hyperlink ref="A84" r:id="rId83"/>
+    <hyperlink ref="A85" r:id="rId84"/>
+    <hyperlink ref="A86" r:id="rId85"/>
+    <hyperlink ref="A87" r:id="rId86"/>
+    <hyperlink ref="A88" r:id="rId87"/>
+    <hyperlink ref="A89" r:id="rId88"/>
+    <hyperlink ref="A90" r:id="rId89"/>
+    <hyperlink ref="A91" r:id="rId90"/>
+    <hyperlink ref="A92" r:id="rId91"/>
+    <hyperlink ref="A93" r:id="rId92"/>
+    <hyperlink ref="A94" r:id="rId93"/>
+    <hyperlink ref="A95" r:id="rId94"/>
+    <hyperlink ref="A96" r:id="rId95"/>
+    <hyperlink ref="A97" r:id="rId96"/>
+    <hyperlink ref="A98" r:id="rId97"/>
+    <hyperlink ref="A99" r:id="rId98"/>
+    <hyperlink ref="A100" r:id="rId99"/>
+    <hyperlink ref="A101" r:id="rId100"/>
+    <hyperlink ref="A102" r:id="rId101"/>
+    <hyperlink ref="A103" r:id="rId102"/>
+    <hyperlink ref="A104" r:id="rId103"/>
+    <hyperlink ref="A105" r:id="rId104"/>
+    <hyperlink ref="A106" r:id="rId105"/>
+    <hyperlink ref="A107" r:id="rId106"/>
+    <hyperlink ref="A108" r:id="rId107"/>
+    <hyperlink ref="A109" r:id="rId108"/>
+    <hyperlink ref="A110" r:id="rId109"/>
+    <hyperlink ref="A111" r:id="rId110"/>
+    <hyperlink ref="A112" r:id="rId111"/>
+    <hyperlink ref="A113" r:id="rId112"/>
+    <hyperlink ref="A114" r:id="rId113"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>